--- a/public/templates/machines_template.xlsx
+++ b/public/templates/machines_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Template" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,23 +397,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>internalCode</v>
       </c>
       <c r="B1" t="str">
-        <v>modelInternalCode</v>
+        <v>description</v>
       </c>
       <c r="C1" t="str">
-        <v>locationInternalCode</v>
+        <v>brand</v>
       </c>
       <c r="D1" t="str">
-        <v>description</v>
+        <v>model</v>
       </c>
       <c r="E1" t="str">
-        <v>properties</v>
+        <v>series</v>
+      </c>
+      <c r="F1" t="str">
+        <v>state</v>
+      </c>
+      <c r="G1" t="str">
+        <v>characteristics</v>
       </c>
     </row>
     <row r="2">
@@ -421,16 +427,22 @@
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>MODEL_X1</v>
+        <v>Main production machine</v>
       </c>
       <c r="C2" t="str">
-        <v>PLANT_A</v>
+        <v>Brand X</v>
       </c>
       <c r="D2" t="str">
-        <v>Main production machine</v>
+        <v>Model X1</v>
       </c>
       <c r="E2" t="str">
-        <v>{"serialNumber":"MX1001","installationDate":"2023-01-15"}</v>
+        <v>Series A</v>
+      </c>
+      <c r="F2" t="str">
+        <v>active</v>
+      </c>
+      <c r="G2" t="str">
+        <v>{"power":"100kW","weight":"500kg","voltage":"220V"}</v>
       </c>
     </row>
     <row r="3">
@@ -438,16 +450,22 @@
         <v/>
       </c>
       <c r="B3" t="str">
-        <v>MODEL_Y2</v>
+        <v>Secondary machine</v>
       </c>
       <c r="C3" t="str">
-        <v>BUILDING_A</v>
+        <v>Brand Y</v>
       </c>
       <c r="D3" t="str">
-        <v>Secondary machine</v>
+        <v>Model Y2</v>
       </c>
       <c r="E3" t="str">
-        <v>{"serialNumber":"MY2002","installationDate":"2023-02-20"}</v>
+        <v>Series B</v>
+      </c>
+      <c r="F3" t="str">
+        <v>active</v>
+      </c>
+      <c r="G3" t="str">
+        <v>{"power":"150kW","weight":"750kg","voltage":"380V"}</v>
       </c>
     </row>
     <row r="4">
@@ -455,21 +473,27 @@
         <v/>
       </c>
       <c r="B4" t="str">
-        <v>MODEL_Z3</v>
+        <v>Backup machine</v>
       </c>
       <c r="C4" t="str">
-        <v>BUILDING_B</v>
+        <v>Brand Z</v>
       </c>
       <c r="D4" t="str">
-        <v>Backup machine</v>
+        <v>Model Z3</v>
       </c>
       <c r="E4" t="str">
-        <v>{"serialNumber":"MZ3003","installationDate":"2023-03-10"}</v>
+        <v>Series C</v>
+      </c>
+      <c r="F4" t="str">
+        <v>inactive</v>
+      </c>
+      <c r="G4" t="str">
+        <v>{"power":"200kW","weight":"1000kg","voltage":"220V"}</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/machines_template.xlsx
+++ b/public/templates/machines_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Template" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:J4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,9 +416,18 @@
         <v>series</v>
       </c>
       <c r="F1" t="str">
+        <v>category</v>
+      </c>
+      <c r="G1" t="str">
+        <v>locationInternalCode</v>
+      </c>
+      <c r="H1" t="str">
+        <v>rootLocationInternalCode</v>
+      </c>
+      <c r="I1" t="str">
         <v>state</v>
       </c>
-      <c r="G1" t="str">
+      <c r="J1" t="str">
         <v>characteristics</v>
       </c>
     </row>
@@ -439,9 +448,18 @@
         <v>Series A</v>
       </c>
       <c r="F2" t="str">
+        <v>Production</v>
+      </c>
+      <c r="G2" t="str">
+        <v>PROD_LINE_1</v>
+      </c>
+      <c r="H2" t="str">
+        <v>PLANT_A</v>
+      </c>
+      <c r="I2" t="str">
         <v>active</v>
       </c>
-      <c r="G2" t="str">
+      <c r="J2" t="str">
         <v>{"power":"100kW","weight":"500kg","voltage":"220V"}</v>
       </c>
     </row>
@@ -462,9 +480,18 @@
         <v>Series B</v>
       </c>
       <c r="F3" t="str">
+        <v>Production</v>
+      </c>
+      <c r="G3" t="str">
+        <v>PROD_LINE_2</v>
+      </c>
+      <c r="H3" t="str">
+        <v>PLANT_A</v>
+      </c>
+      <c r="I3" t="str">
         <v>active</v>
       </c>
-      <c r="G3" t="str">
+      <c r="J3" t="str">
         <v>{"power":"150kW","weight":"750kg","voltage":"380V"}</v>
       </c>
     </row>
@@ -485,15 +512,24 @@
         <v>Series C</v>
       </c>
       <c r="F4" t="str">
+        <v>Maintenance</v>
+      </c>
+      <c r="G4" t="str">
+        <v>WAREHOUSE</v>
+      </c>
+      <c r="H4" t="str">
+        <v>PLANT_A</v>
+      </c>
+      <c r="I4" t="str">
         <v>inactive</v>
       </c>
-      <c r="G4" t="str">
+      <c r="J4" t="str">
         <v>{"power":"200kW","weight":"1000kg","voltage":"220V"}</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/machines_template.xlsx
+++ b/public/templates/machines_template.xlsx
@@ -419,10 +419,10 @@
         <v>category</v>
       </c>
       <c r="G1" t="str">
-        <v>locationInternalCode</v>
+        <v>locationName</v>
       </c>
       <c r="H1" t="str">
-        <v>rootLocationInternalCode</v>
+        <v>rootLocationName</v>
       </c>
       <c r="I1" t="str">
         <v>state</v>
@@ -451,10 +451,10 @@
         <v>Production</v>
       </c>
       <c r="G2" t="str">
-        <v>PROD_LINE_1</v>
+        <v>Production Line 1</v>
       </c>
       <c r="H2" t="str">
-        <v>PLANT_A</v>
+        <v>Plant A</v>
       </c>
       <c r="I2" t="str">
         <v>active</v>
@@ -483,10 +483,10 @@
         <v>Production</v>
       </c>
       <c r="G3" t="str">
-        <v>PROD_LINE_2</v>
+        <v>Production Line 2</v>
       </c>
       <c r="H3" t="str">
-        <v>PLANT_A</v>
+        <v>Plant A</v>
       </c>
       <c r="I3" t="str">
         <v>active</v>
@@ -515,10 +515,10 @@
         <v>Maintenance</v>
       </c>
       <c r="G4" t="str">
-        <v>WAREHOUSE</v>
+        <v>Warehouse Section</v>
       </c>
       <c r="H4" t="str">
-        <v>PLANT_A</v>
+        <v>Plant A</v>
       </c>
       <c r="I4" t="str">
         <v>inactive</v>

--- a/public/templates/machines_template.xlsx
+++ b/public/templates/machines_template.xlsx
@@ -460,7 +460,7 @@
         <v>active</v>
       </c>
       <c r="J2" t="str">
-        <v>{"power":"100kW","weight":"500kg","voltage":"220V"}</v>
+        <v>power:100kW;weight:500kg;voltage:220V</v>
       </c>
     </row>
     <row r="3">
@@ -492,7 +492,7 @@
         <v>active</v>
       </c>
       <c r="J3" t="str">
-        <v>{"power":"150kW","weight":"750kg","voltage":"380V"}</v>
+        <v>power:150kW;weight:750kg;voltage:380V</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +524,7 @@
         <v>inactive</v>
       </c>
       <c r="J4" t="str">
-        <v>{"power":"200kW","weight":"1000kg","voltage":"220V"}</v>
+        <v>power:200kW;weight:1000kg;voltage:220V</v>
       </c>
     </row>
   </sheetData>
